--- a/Result/checksun_type/光碟片.xlsx
+++ b/Result/checksun_type/光碟片.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>217717</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>149413</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>216732</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>221658</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>301588</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>199194</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>216632</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>357016</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>609988</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>600689</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>797538</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>321219</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>681031</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>11.35</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>12.17</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>12.17</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>6374586.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>6276306.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>6276306.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>6172143.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>6120482.7</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>6120482.7</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>1092.670297188684</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>6374586</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>6374586.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>11.34</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>11.72</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>12.18</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>12.18</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>5083810.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>6319570.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>6319570</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>6371532.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>6286789.12</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>6286789.12</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-37280.49329111539</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>5083810</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>5083810.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>11.35</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>11.76</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>4306252.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>6287787.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>6287787.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>6337176.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>6317197.72</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>6317197.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>47529.57634313405</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>4306252</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>4306252.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>11.41</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>11.82</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>12.23</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>6012740.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>6822854.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>6822854.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>6396052.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>6383487.3</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>6383487.3</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>250299.1195226638</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>6012740</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>6012740.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>11.56</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>11.88</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>12.27</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>12.27</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>9604144.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>6652897.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>6652897</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>6544709.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>6396298.78</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>6396298.78</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>348192.641224754</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>9604144</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>9604144.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>11.71</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>12.3</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>6590904.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>6067980.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>6067980.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>5954925.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>6335160.3</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>6335160.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>90811.7921839999</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>6590904</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>6590904.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>11.78</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>11.98</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>12.32</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>12.32</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>4924899.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>6423495.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>6423495.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>5851770.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>6272396.72</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>6272396.72</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>42728.72954778001</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>4924899</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>4924899.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>11.81</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>12.35</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>6981584.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>6386564.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>6386564.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>5914933.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>6303146.3</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>6303146.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>151013.1497264737</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>6981584</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>6981584.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>11.8</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>12.06</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>12.36</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>5162954.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>5969251.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>5969251</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>6029633.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>6293954.36</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>6293954.36</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>79952.74463437591</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>5162954</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>5162954.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>11.73</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>12.37</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>12.37</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>6679560.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>6436521.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>6436521.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>5899216.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>6366925.96</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>6366925.96</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>170435.6393372938</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>6679560</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>6679560.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>11.72</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>12.08</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>12.39</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>12.39</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>8368479.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>5841870.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>5841870.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>5487268.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>6395266.78</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>6395266.78</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>131116.4303651303</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>8368479</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>8368479.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>13.99</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>13.56</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>13.16</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>13.16</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>14268504.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>7249024.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>7249024</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>4013502.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1806762.58</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1806762.58</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>1860277.105062644</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>14268504</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>14268504.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>13.77</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>13.48</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>13.13</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>13.13</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>19324917.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>4474500.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>4474500.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2680782.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1559186.4</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1559186.4</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>1298075.861681122</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>19324917</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>19324917.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>13.6</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>13.42</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>13.12</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>13.12</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>747352.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>738435.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>738435.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>889759.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1194825.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1194825</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-93187.15963823383</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>747352</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>747352.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>13.73</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>13.44</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>13.13</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>13.13</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>890136.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>963018.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>963018</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1200071.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1209385.54</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1209385.54</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-86924.25582166249</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>890136</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>890136.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>13.72</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>13.14</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>13.14</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1014211.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>826858.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>826858.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1204934.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1209173.9</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1209173.9</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-90171.0983757868</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1014211</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1014211.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>13.76</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>13.36</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>13.15</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>395887.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>777981.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>777981</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1295516.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1214275.24</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1214275.24</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-104882.7985111149</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>395887</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>395887.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>13.84</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>13.16</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>13.16</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>644591.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>887064.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>887064.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1310132.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1256904.46</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1256904.46</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-55904.69875761541</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>644591</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>644591.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>13.8</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>13.18</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>13.18</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>1870265.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1041083.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1041083.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1295875.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1300658.24</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1300658.24</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-10586.24558270094</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1870265</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1870265.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>13.74</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>13.17</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>13.17</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>209340.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1437124.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1437124.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1160130.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1291148.76</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1291148.76</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-76789.73227629834</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>209340</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>209340.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>13.68</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>13.17</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>13.17</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>769822.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1583011.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1583011</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1216033.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1347530.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1347530</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>9332.598599859048</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>769822</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>769822.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>13.56</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>13.02</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>13.19</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>13.19</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>941304.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1813051.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1813051</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1258842.7</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1473262.06</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1473262.06</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>71979.5499015178</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>941304</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>941304.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>8.82</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>9.86</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>9.859999999999999</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>9972293.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>14369421.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>14369421</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>17558033.3</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>19048623.2</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>19048623.2</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1306259.625022756</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>9972293</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>9972293.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>8.831999999999999</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>9.39</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>9.89</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>9.890000000000001</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>13596266.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>14471442.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>14471442</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>18603295.3</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>20344230.52</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>20344230.52</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-894175.6758462638</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>13596266</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>13596266.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>8.858</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>9.45</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>9.94</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>16650289.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>16478823.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>16478823.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>19578158.0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>20527960.6</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>20527960.6</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-661832.295742482</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>16650289</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>16650289.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>8.926</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>9.51</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>9.99</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>9.99</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>17661962.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>17066764.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>17066764.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>18899159.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>20840462.66</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>20840462.66</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-633493.0636034198</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>17661962</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>17661962.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>9.006</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>9.56</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>10.04</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>10.04</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>13966295.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>18383722.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>18383722</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>18585920.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>21263844.96</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>21263844.96</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-678777.2297046371</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>13966295</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>13966295.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>9.110000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>9.61</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>10.09</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>10.09</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>10482398.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>20746645.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>20746645.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>18861049.3</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>22775540.76</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>22775540.76</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-323262.5302169211</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>10482398</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>10482398.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>9.251999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>9.66</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>10.14</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>10.14</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>23633175.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>22735148.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>22735148.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>19734371.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>23181075.62</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>23181075.62</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>569435.3808447011</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>23633175</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>23633175.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>9.358</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>9.71</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>10.18</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>19589992.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>22677492.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>22677492.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>20403553.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>22942154.96</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>22942154.96</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>415369.3116168492</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>19589992</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>19589992.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>9.486</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>9.76</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>10.21</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>10.21</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>24246750.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>20731554.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>20731554</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>20540852.2</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>23073858.1</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>23073858.1</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>613638.4873050377</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>24246750</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>24246750.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>9.568000000000001</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>10.25</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>25780913.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>18788118.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>18788118</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>21895847.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>23100469.96</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>23100469.96</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>376026.1494558416</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>25780913</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>25780913.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>9.639999999999999</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>9.82</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>10.28</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>20424913.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>16975453.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>16975453</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>20739984.6</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>23033816.78</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>23033816.78</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-141224.1599521525</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>20424913</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>20424913.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>9.228</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>25413025.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>29524861.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>29524861.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>39980490.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>39672124.82</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>39672124.82</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-3607709.71721825</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>25413025</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>25413025.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>9.192</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>9.19</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>9.19</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>36288082.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>32197610.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>32197610.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>48861025.8</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>40048200.52</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>40048200.52</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-2966272.789255016</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>36288082</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>36288082.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>9.208000000000002</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>9.34</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>9.18</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>22788815.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>32206845.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>32206845.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>49654108.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>40246339.64</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>40246339.64</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-3109180.685405575</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>22788815</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>22788815.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>9.326</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>9.18</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>34574440.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>37008593.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>37008593.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>51527173.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>41695798.62</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>41695798.62</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-1755942.619713314</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>34574440</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>34574440.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>9.414000000000001</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>9.18</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>28559944.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>37089506.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>37089506</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>54638352.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>47573634.92</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>47573634.92</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-1022778.682306044</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>28559944</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>28559944.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>9.448</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>9.18</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>38776773.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>50436120.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>50436120.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>61444441.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>48893469.38</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>48893469.38</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>705536.4669295549</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>38776773</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>38776773.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>9.594</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>9.17</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>9.17</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>36334255.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>65524440.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>65524440.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>59980228.3</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>48654493.06</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>48654493.06</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>2054700.127732933</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>36334255</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>36334255.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>9.618</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>9.16</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>9.16</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>46797556.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>67101372.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>67101372.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>59298794.7</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>48765466.16</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>48765466.16</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>4170392.995747298</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>46797556</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>46797556.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>9.588</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>9.31</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>9.14</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>9.140000000000001</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>34979002.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>66045753.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>66045753.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>56515326.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>48604939.26</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>48604939.26</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>5922800.807348274</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>34979002</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>34979002.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>9.6</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>9.29</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>9.13</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>9.130000000000001</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>95293016.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>72187199.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>72187199.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>56586574.1</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>48888014.02</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>48888014.02</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>9480985.580801517</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>95293016</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>95293016.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>9.598</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>9.27</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>9.12</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>9.119999999999999</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>114218375.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>72452763.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>72452763.40000001</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>50955267.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>47803652.84</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>47803652.84</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>7763284.272134669</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>114218375</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>114218375.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
